--- a/artfynd/A 40677-2024 artfynd.xlsx
+++ b/artfynd/A 40677-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120778990</v>
+        <v>120785077</v>
       </c>
       <c r="B2" t="n">
-        <v>79680</v>
+        <v>90458</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>3215</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,14 +714,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gammal sälg, Jmt</t>
+          <t>Myrkant, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>453628</v>
+        <v>453855</v>
       </c>
       <c r="R2" t="n">
-        <v>6989192</v>
+        <v>6988791</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -753,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120785077</v>
+        <v>120778990</v>
       </c>
       <c r="B3" t="n">
-        <v>90458</v>
+        <v>79680</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3215</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -830,14 +830,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Myrkant, Jmt</t>
+          <t>Gammal sälg, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>453855</v>
+        <v>453628</v>
       </c>
       <c r="R3" t="n">
-        <v>6988791</v>
+        <v>6989192</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -869,7 +869,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120779027</v>
+        <v>120779020</v>
       </c>
       <c r="B4" t="n">
-        <v>79680</v>
+        <v>79679</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>453763</v>
+        <v>453755</v>
       </c>
       <c r="R4" t="n">
-        <v>6988976</v>
+        <v>6988978</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120779020</v>
+        <v>120779027</v>
       </c>
       <c r="B5" t="n">
-        <v>79679</v>
+        <v>79680</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,21 +1039,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>453755</v>
+        <v>453763</v>
       </c>
       <c r="R5" t="n">
-        <v>6988978</v>
+        <v>6988976</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
